--- a/D2004_radiogenic.xlsx
+++ b/D2004_radiogenic.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\altar\Desktop\project listhospheric mantle\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\altar\Desktop\project central anatolia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB4E277-5A7E-4C33-8B6B-13442AA7EE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D514804-2090-49CA-B3DC-96FB08214BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -114,7 +125,7 @@
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,6 +198,15 @@
       <name val="Verdana"/>
       <family val="2"/>
       <charset val="162"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -238,12 +258,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -278,6 +292,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -561,12 +581,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -601,193 +621,205 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="18">
         <v>0.70365599999999995</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="18">
         <v>0.70368399999999998</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="7">
+      <c r="D2" s="19">
+        <v>0.70487724786313954</v>
+      </c>
+      <c r="E2" s="19">
+        <v>0.70519202553894811</v>
+      </c>
+      <c r="F2" s="19">
+        <v>0.70439323330816039</v>
+      </c>
+      <c r="G2" s="19">
+        <v>0.70515396823679044</v>
+      </c>
+      <c r="H2" s="18">
         <v>0.70394199999999996</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="18">
         <v>0.70390200000000003</v>
       </c>
-      <c r="J2" s="10"/>
-    </row>
-    <row r="3" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
+      <c r="J2" s="19">
+        <v>0.70521846636237961</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="10">
         <v>0.51282292050202094</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="10">
         <v>0.51281821971764985</v>
       </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="12">
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="10">
         <v>0.51281301892732323</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="10">
         <v>0.51280744794612043</v>
       </c>
-      <c r="J3" s="10"/>
-    </row>
-    <row r="4" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="13" t="s">
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:11" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="12">
         <v>38.983600223927589</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="12">
         <v>38.983208686293978</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="14">
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="12">
         <v>38.991181848548202</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="12">
         <v>38.989011523799782</v>
       </c>
-      <c r="J4" s="10"/>
-    </row>
-    <row r="5" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:11" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="12">
         <v>15.652700920860482</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="12">
         <v>15.652658881502811</v>
       </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="14">
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="12">
         <v>15.656141430006061</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="12">
         <v>15.663260300475008</v>
       </c>
-      <c r="J5" s="10"/>
-    </row>
-    <row r="6" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:11" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="12">
         <v>18.968785843169069</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="12">
         <v>18.969210672226506</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="14">
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="12">
         <v>18.968206066902329</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="12">
         <v>18.948793376591986</v>
       </c>
-      <c r="J6" s="10"/>
-    </row>
-    <row r="7" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="15" t="s">
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:11" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="14">
         <f>(0.1084*B6)+13.491</f>
         <v>15.547216385399526</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="14">
         <f>(0.1084*C6)+13.491</f>
         <v>15.547262436869353</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="16">
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="14">
         <f>(0.1084*H6)+13.491</f>
         <v>15.547153537652212</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="14">
         <f>(0.1084*I6)+13.491</f>
         <v>15.545049202022572</v>
       </c>
-      <c r="J7" s="10"/>
-    </row>
-    <row r="8" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="15" t="s">
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:11" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="14">
         <f>(1.209*B6)+15.627</f>
         <v>38.560262084391404</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="14">
         <f>(1.209*C6)+15.627</f>
         <v>38.560775702721848</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="16">
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="14">
         <f>(1.209*H6)+15.627</f>
         <v>38.559561134884916</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="14">
         <f>(1.209*I6)+15.627</f>
         <v>38.536091192299715</v>
       </c>
-      <c r="J8" s="10"/>
-    </row>
-    <row r="9" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="17" t="s">
+      <c r="J8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="16">
         <v>0.28300709047155537</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="16">
         <v>0.28300483809712151</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="18">
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="16">
         <v>0.28300933728620442</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="16">
         <v>0.28301023744090276</v>
       </c>
-      <c r="J9" s="10"/>
-    </row>
-    <row r="10" spans="1:11" s="8" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:11" s="6" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="17">
         <v>8.3137818297185362</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="17">
         <v>8.2341284540721205</v>
       </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="19">
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="17">
         <v>8.3932385881335669</v>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="17">
         <v>8.425071821209773</v>
       </c>
-      <c r="J10" s="10"/>
+      <c r="J10" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
